--- a/Config/Hero.xlsx
+++ b/Config/Hero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9853A9E4-A315-4E88-9DF4-5912C246C993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85B8B34-B409-4098-8DCD-C11B595AD738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-750" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="510" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2,9</t>
+    <t>2,10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Config/Hero.xlsx
+++ b/Config/Hero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85B8B34-B409-4098-8DCD-C11B595AD738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0075D45-50F8-40B0-B986-30AC0CB41942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="510" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22020" yWindow="2475" windowWidth="21855" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -132,6 +132,22 @@
   </si>
   <si>
     <t>2,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WinAnimID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoseAnimID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胜利动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失败动画</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -185,7 +201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -194,6 +210,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -461,15 +478,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.08984375" customWidth="1"/>
     <col min="4" max="6" width="15.90625" customWidth="1"/>
     <col min="7" max="7" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" customWidth="1"/>
+    <col min="10" max="10" width="11.08984375" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +499,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,9 +528,14 @@
       <c r="J2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -538,8 +564,14 @@
       <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,8 +602,14 @@
       <c r="J4" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -599,8 +637,14 @@
       <c r="J5">
         <v>6012</v>
       </c>
+      <c r="K5">
+        <v>6013</v>
+      </c>
+      <c r="L5">
+        <v>6014</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -622,8 +666,14 @@
       <c r="J6">
         <v>6002</v>
       </c>
+      <c r="K6">
+        <v>6013</v>
+      </c>
+      <c r="L6">
+        <v>6014</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -645,8 +695,14 @@
       <c r="J7">
         <v>6002</v>
       </c>
+      <c r="K7">
+        <v>6013</v>
+      </c>
+      <c r="L7">
+        <v>6014</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
@@ -667,6 +723,12 @@
       </c>
       <c r="J8">
         <v>6012</v>
+      </c>
+      <c r="K8">
+        <v>6013</v>
+      </c>
+      <c r="L8">
+        <v>6014</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Hero.xlsx
+++ b/Config/Hero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0075D45-50F8-40B0-B986-30AC0CB41942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2905A-54A3-4F08-A073-7F21F37426B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22020" yWindow="2475" windowWidth="21855" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -210,7 +210,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -567,7 +566,7 @@
       <c r="K3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -602,10 +601,10 @@
       <c r="J4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -658,7 +657,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>3051</v>
+        <v>3001</v>
       </c>
       <c r="I6">
         <v>6001</v>
@@ -687,7 +686,7 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>3051</v>
+        <v>3001</v>
       </c>
       <c r="I7">
         <v>6001</v>

--- a/Config/Hero.xlsx
+++ b/Config/Hero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2905A-54A3-4F08-A073-7F21F37426B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4854CE6-E5A7-4F46-ABB6-FC9FDF684688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21705" yWindow="-3480" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -148,6 +148,10 @@
   </si>
   <si>
     <t>失败动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试飞剑小兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.08984375" customWidth="1"/>
@@ -730,6 +734,35 @@
         <v>6014</v>
       </c>
     </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3001</v>
+      </c>
+      <c r="I9">
+        <v>6001</v>
+      </c>
+      <c r="J9">
+        <v>6002</v>
+      </c>
+      <c r="K9">
+        <v>6013</v>
+      </c>
+      <c r="L9">
+        <v>6014</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
